--- a/data/trans_orig/CoTrAQ-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/CoTrAQ-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2012</t>
+          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21767</t>
+          <t>22729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44497</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>29974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39188</t>
+          <t>39766</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67956</t>
+          <t>68575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28322</t>
+          <t>29284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53171</t>
+          <t>54168</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>15402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34323</t>
+          <t>33848</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51143</t>
+          <t>50247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81434</t>
+          <t>80649</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179498</t>
+          <t>178560</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>210321</t>
+          <t>209043</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>98335</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120599</t>
+          <t>121177</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>284831</t>
+          <t>285001</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>323008</t>
+          <t>324007</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,86%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43179</t>
+          <t>44443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72993</t>
+          <t>73794</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29795</t>
+          <t>30746</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54574</t>
+          <t>54998</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81310</t>
+          <t>82304</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120851</t>
+          <t>120142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>37521</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66940</t>
+          <t>66227</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32867</t>
+          <t>32095</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58248</t>
+          <t>56005</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>76413</t>
+          <t>76267</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>112181</t>
+          <t>112701</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>270568</t>
+          <t>269675</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>306075</t>
+          <t>308595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156163</t>
+          <t>157169</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>187603</t>
+          <t>186623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>439706</t>
+          <t>439170</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>487524</t>
+          <t>485355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>30424</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>56291</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26132</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49664</t>
+          <t>51886</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64188</t>
+          <t>63905</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>98827</t>
+          <t>99750</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36359</t>
+          <t>37361</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62490</t>
+          <t>64058</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23131</t>
+          <t>24285</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45887</t>
+          <t>47379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65317</t>
+          <t>65494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101907</t>
+          <t>100918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>200350</t>
+          <t>199294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>233011</t>
+          <t>232591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117548</t>
+          <t>117442</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146313</t>
+          <t>146023</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>323947</t>
+          <t>327570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>370765</t>
+          <t>371271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,48%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39860</t>
+          <t>40184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66917</t>
+          <t>66766</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41686</t>
+          <t>41872</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72256</t>
+          <t>69184</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88596</t>
+          <t>89241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130767</t>
+          <t>125932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60549</t>
+          <t>61162</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92973</t>
+          <t>93292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43785</t>
+          <t>43106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70911</t>
+          <t>69965</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111807</t>
+          <t>112215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152018</t>
+          <t>153522</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>257303</t>
+          <t>258072</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>296576</t>
+          <t>295467</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158999</t>
+          <t>160242</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>193832</t>
+          <t>194428</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>427172</t>
+          <t>429740</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>479203</t>
+          <t>478312</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,95%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157107</t>
+          <t>159502</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>210326</t>
+          <t>214712</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>130100</t>
+          <t>132265</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>178100</t>
+          <t>181322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>303929</t>
+          <t>304159</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>377817</t>
+          <t>375033</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>188932</t>
+          <t>190051</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>243656</t>
+          <t>247193</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135744</t>
+          <t>134966</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>182130</t>
+          <t>179078</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>338714</t>
+          <t>337359</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>410745</t>
+          <t>411728</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>944619</t>
+          <t>944768</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1016884</t>
+          <t>1016177</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>562098</t>
+          <t>563741</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>620915</t>
+          <t>621024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1525136</t>
+          <t>1521554</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1613385</t>
+          <t>1616962</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2016</t>
+          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44360</t>
+          <t>44729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71387</t>
+          <t>71849</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37363</t>
+          <t>37311</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60436</t>
+          <t>58960</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88272</t>
+          <t>88512</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123962</t>
+          <t>123048</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32800</t>
+          <t>32692</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55753</t>
+          <t>56145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27362</t>
+          <t>27843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48836</t>
+          <t>48949</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66750</t>
+          <t>65400</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97638</t>
+          <t>96952</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>126065</t>
+          <t>126585</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>158027</t>
+          <t>156862</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69001</t>
+          <t>68712</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>94370</t>
+          <t>93634</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>203861</t>
+          <t>204669</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>244010</t>
+          <t>245234</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,72%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72287</t>
+          <t>72927</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107815</t>
+          <t>107818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54971</t>
+          <t>54267</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84680</t>
+          <t>84941</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138793</t>
+          <t>135549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181129</t>
+          <t>183273</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73356</t>
+          <t>73900</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>106919</t>
+          <t>107230</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50741</t>
+          <t>51237</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78219</t>
+          <t>78363</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>132998</t>
+          <t>134907</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>179399</t>
+          <t>178345</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>212977</t>
+          <t>212621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>255976</t>
+          <t>254095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124900</t>
+          <t>123362</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157831</t>
+          <t>158065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>348245</t>
+          <t>348621</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>400595</t>
+          <t>404927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105570</t>
+          <t>105164</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145140</t>
+          <t>142625</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78378</t>
+          <t>80740</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110505</t>
+          <t>113212</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>193931</t>
+          <t>195614</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>245140</t>
+          <t>242600</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75497</t>
+          <t>76657</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112621</t>
+          <t>111622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49420</t>
+          <t>48172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77879</t>
+          <t>75916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133641</t>
+          <t>135876</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177752</t>
+          <t>178083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127202</t>
+          <t>127201</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165089</t>
+          <t>165502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96713</t>
+          <t>97280</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129232</t>
+          <t>127924</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235381</t>
+          <t>233724</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>286821</t>
+          <t>281748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>44,41%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57712</t>
+          <t>58750</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89235</t>
+          <t>90486</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68249</t>
+          <t>71186</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102452</t>
+          <t>103936</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138204</t>
+          <t>138461</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>183740</t>
+          <t>181376</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62224</t>
+          <t>62022</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93843</t>
+          <t>92986</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43811</t>
+          <t>44999</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71978</t>
+          <t>70434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113945</t>
+          <t>113890</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>158684</t>
+          <t>157314</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -4837,12 +4837,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>230815</t>
+          <t>231330</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>270420</t>
+          <t>269114</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164355</t>
+          <t>164515</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>200833</t>
+          <t>200005</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>405810</t>
+          <t>405525</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>460964</t>
+          <t>458564</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,11%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>310145</t>
+          <t>312169</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>377952</t>
+          <t>377903</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>268682</t>
+          <t>269613</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>328058</t>
+          <t>329225</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>600016</t>
+          <t>597361</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>689283</t>
+          <t>688323</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>273836</t>
+          <t>273677</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>338540</t>
+          <t>335916</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>198462</t>
+          <t>196384</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>249988</t>
+          <t>250339</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>486137</t>
+          <t>484041</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>564097</t>
+          <t>573467</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -5293,12 +5293,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>736066</t>
+          <t>737475</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>812043</t>
+          <t>811516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>484910</t>
+          <t>485112</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>549948</t>
+          <t>549827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1239983</t>
+          <t>1244271</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1340572</t>
+          <t>1340367</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CoTrAQ-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/CoTrAQ-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22729</t>
+          <t>22897</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43928</t>
+          <t>45019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29974</t>
+          <t>30062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39766</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68575</t>
+          <t>67365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29284</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54168</t>
+          <t>53024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>16682</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33848</t>
+          <t>35723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50247</t>
+          <t>49480</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80649</t>
+          <t>81361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>178560</t>
+          <t>178423</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>209043</t>
+          <t>208753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98335</t>
+          <t>98174</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>121177</t>
+          <t>121296</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>285001</t>
+          <t>285564</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>324007</t>
+          <t>323578</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44443</t>
+          <t>42843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73794</t>
+          <t>72213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30746</t>
+          <t>29805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54998</t>
+          <t>54323</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82304</t>
+          <t>80113</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120142</t>
+          <t>120284</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37521</t>
+          <t>37799</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66227</t>
+          <t>66822</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>33073</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56005</t>
+          <t>57124</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>76267</t>
+          <t>76284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>112701</t>
+          <t>113988</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>269675</t>
+          <t>270543</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>308595</t>
+          <t>307830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157169</t>
+          <t>155296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186623</t>
+          <t>188035</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>439170</t>
+          <t>437332</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>485355</t>
+          <t>486219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,12%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30424</t>
+          <t>29684</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56291</t>
+          <t>55836</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28622</t>
+          <t>26489</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51886</t>
+          <t>50149</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63905</t>
+          <t>63099</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>99750</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37361</t>
+          <t>35484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64058</t>
+          <t>62623</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24285</t>
+          <t>23216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47379</t>
+          <t>46352</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65494</t>
+          <t>65661</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100918</t>
+          <t>100704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199294</t>
+          <t>199299</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>232591</t>
+          <t>232314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117442</t>
+          <t>118252</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146023</t>
+          <t>146704</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>327570</t>
+          <t>326026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>371271</t>
+          <t>371240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40184</t>
+          <t>39842</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66766</t>
+          <t>68637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41872</t>
+          <t>41980</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69184</t>
+          <t>71560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89241</t>
+          <t>87367</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125932</t>
+          <t>127859</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61162</t>
+          <t>60646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93292</t>
+          <t>91894</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43106</t>
+          <t>43414</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69965</t>
+          <t>69759</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112215</t>
+          <t>111313</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153522</t>
+          <t>154469</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>258072</t>
+          <t>258033</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>295467</t>
+          <t>295468</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>160242</t>
+          <t>158108</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>194428</t>
+          <t>192173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>429740</t>
+          <t>428611</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>478312</t>
+          <t>480002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,2%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>159502</t>
+          <t>159331</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214712</t>
+          <t>209965</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>132265</t>
+          <t>131060</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>181322</t>
+          <t>178080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>304159</t>
+          <t>305181</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>375033</t>
+          <t>373668</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>190051</t>
+          <t>189788</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>247193</t>
+          <t>246228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>134966</t>
+          <t>136060</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>179078</t>
+          <t>184050</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>337359</t>
+          <t>333165</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>411728</t>
+          <t>411520</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>944768</t>
+          <t>945134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1016177</t>
+          <t>1012419</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>563741</t>
+          <t>562357</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>621024</t>
+          <t>620636</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1521554</t>
+          <t>1526867</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1616962</t>
+          <t>1620120</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44729</t>
+          <t>44794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71849</t>
+          <t>70727</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37311</t>
+          <t>36913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58960</t>
+          <t>60568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88512</t>
+          <t>88072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123048</t>
+          <t>125204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32692</t>
+          <t>33666</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56145</t>
+          <t>57077</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27843</t>
+          <t>27669</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48949</t>
+          <t>50040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65400</t>
+          <t>65805</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96952</t>
+          <t>97334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>126585</t>
+          <t>126989</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156862</t>
+          <t>157892</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68712</t>
+          <t>67506</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93634</t>
+          <t>93290</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>204669</t>
+          <t>203936</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>245234</t>
+          <t>245287</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,73%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72927</t>
+          <t>75184</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107818</t>
+          <t>109377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54267</t>
+          <t>54437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84941</t>
+          <t>83618</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135549</t>
+          <t>134584</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183273</t>
+          <t>181218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73900</t>
+          <t>73184</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>107230</t>
+          <t>108111</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>51480</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78363</t>
+          <t>79082</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>134907</t>
+          <t>132542</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>178345</t>
+          <t>177378</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>212621</t>
+          <t>212677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>254095</t>
+          <t>253300</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123362</t>
+          <t>124237</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158065</t>
+          <t>159535</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>348621</t>
+          <t>349303</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>404927</t>
+          <t>401346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,35%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105164</t>
+          <t>104865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>142625</t>
+          <t>143267</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80740</t>
+          <t>81364</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113212</t>
+          <t>111589</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>195614</t>
+          <t>195790</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>242600</t>
+          <t>245413</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76657</t>
+          <t>76403</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111622</t>
+          <t>109966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48172</t>
+          <t>50288</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75916</t>
+          <t>77281</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>135876</t>
+          <t>133556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178083</t>
+          <t>179372</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127201</t>
+          <t>129313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165502</t>
+          <t>166026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97280</t>
+          <t>97740</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127924</t>
+          <t>128239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>233724</t>
+          <t>233563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>281748</t>
+          <t>282854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58750</t>
+          <t>57119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90486</t>
+          <t>86568</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71186</t>
+          <t>70311</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103936</t>
+          <t>103092</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138461</t>
+          <t>135788</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>181376</t>
+          <t>182197</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62022</t>
+          <t>62584</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92986</t>
+          <t>94185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44999</t>
+          <t>44922</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70434</t>
+          <t>72452</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113890</t>
+          <t>114947</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>157314</t>
+          <t>155954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -4837,12 +4837,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>231330</t>
+          <t>232798</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>269114</t>
+          <t>269129</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164515</t>
+          <t>162548</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>200005</t>
+          <t>201008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>405525</t>
+          <t>407887</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>458564</t>
+          <t>461358</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,49%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>312169</t>
+          <t>310752</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>377903</t>
+          <t>377615</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269613</t>
+          <t>271231</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>329225</t>
+          <t>327797</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>597361</t>
+          <t>599114</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>688323</t>
+          <t>687936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>273677</t>
+          <t>275003</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>335916</t>
+          <t>334427</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>196384</t>
+          <t>194801</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>250339</t>
+          <t>250623</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>484041</t>
+          <t>484770</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>573467</t>
+          <t>567940</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -5293,12 +5293,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>737475</t>
+          <t>736907</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>811516</t>
+          <t>811385</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>485112</t>
+          <t>483378</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>549827</t>
+          <t>554116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1244271</t>
+          <t>1236812</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1340367</t>
+          <t>1340746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,51%</t>
         </is>
       </c>
     </row>
